--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -451,22 +451,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Internship Project Management (m/f/d)</t>
+          <t>(Senior) Program &amp; Project Manager Business Operations (m/f/d)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Publicis One Touch</t>
+          <t>Riverty</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Hamburg, Hamburg, Germany</t>
+          <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4380083981</t>
+          <t>https://www.linkedin.com/jobs/view/4348932306</t>
         </is>
       </c>
     </row>
@@ -478,61 +478,57 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Geek+</t>
+          <t>Westinghouse Electric Company</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Düsseldorf, North Rhine-Westphalia, Germany</t>
+          <t>Mannheim, Baden-Württemberg, Germany</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4422013065</t>
+          <t>https://www.linkedin.com/jobs/view/4326351385</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Project Manager (Germany)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>QCS Staffing</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Berlin, Berlin, Germany</t>
-        </is>
-      </c>
+          <t>Indero (formerly Innovaderm)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4409629041</t>
+          <t>https://www.linkedin.com/jobs/view/4412198959</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Project Manager - Remote Work</t>
+          <t>Internship Project Management (m/f/d)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BairesDev</t>
+          <t>Publicis One Touch</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Berlin, Germany</t>
+          <t>Hamburg, Hamburg, Germany</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4422005429</t>
+          <t>https://www.linkedin.com/jobs/view/4380083981</t>
         </is>
       </c>
     </row>
@@ -544,79 +540,79 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>First Point Group</t>
+          <t>Geek+</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Augsburg, Bavaria, Germany</t>
+          <t>Düsseldorf, North Rhine-Westphalia, Germany</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4417932063</t>
+          <t>https://www.linkedin.com/jobs/view/4422013065</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Creative Project Manager</t>
+          <t>Project Manager - Remote Work</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Designity</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>BairesDev</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4415213744</t>
+          <t>https://www.linkedin.com/jobs/view/4422005429</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Program Manager / Projektmanager Automotiv (all gender)</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ALTEN Germany</t>
+          <t>QCS Staffing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Munich, Bavaria, Germany</t>
+          <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4400833451</t>
+          <t>https://www.linkedin.com/jobs/view/4409629041</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Project Coordinator (m/w/d)</t>
+          <t>Creative Project Manager</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>epay, a Euronet Company</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Martinsried, Bavaria, Germany</t>
-        </is>
-      </c>
+          <t>Designity</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4420902663</t>
+          <t>https://www.linkedin.com/jobs/view/4415213744</t>
         </is>
       </c>
     </row>
@@ -641,212 +637,216 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Program Manager (all genders)</t>
+          <t>Program Manager / Projektmanager Automotiv (all gender)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Impossible Founders</t>
+          <t>ALTEN Germany</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hamburg, Hamburg, Germany</t>
+          <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4417955542</t>
+          <t>https://www.linkedin.com/jobs/view/4400833451</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PMO Manager (Project Management Office) - Yoshi en (all genders)</t>
+          <t>Program Manager (all genders)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sunday Natural</t>
+          <t>Impossible Founders</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Berlin, Berlin, Germany</t>
+          <t>Hamburg, Hamburg, Germany</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4417942812</t>
+          <t>https://www.linkedin.com/jobs/view/4417955542</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Project Manager (Straßenbaumeister)</t>
+          <t>PMO Manager (Project Management Office) - Yoshi en (all genders)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Manning Global AG</t>
+          <t>Sunday Natural</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Frankfurt am Main, Hesse, Germany</t>
+          <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4417945912</t>
+          <t>https://www.linkedin.com/jobs/view/4417942812</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Scheduler (m/w/d)</t>
+          <t>Project Manager (Straßenbaumeister)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>STAR Specialists</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>Manning Global AG</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Frankfurt am Main, Hesse, Germany</t>
+        </is>
+      </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4415386505</t>
+          <t>https://www.linkedin.com/jobs/view/4417945912</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Associate Project Coordinator</t>
+          <t>Senior Project Manager</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Alpha Variance Solutions</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>NetZero</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4417696257</t>
+          <t>https://www.linkedin.com/jobs/view/4420960325</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Project Manager</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NetZero</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Berlin, Germany</t>
+          <t>Stuttgart, Baden-Württemberg, Germany</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4420960325</t>
+          <t>https://www.linkedin.com/jobs/view/4389905806</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Project Manager (m/f/x)</t>
+          <t>Internship Project Management (m/f/d)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Grob Aircraft SE</t>
+          <t>Publicis One Touch</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tussenhausen, Bavaria, Germany</t>
+          <t>Hamburg, Hamburg, Germany</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4411461348</t>
+          <t>https://www.linkedin.com/jobs/view/4380098306</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Project Manager (m/w/d)</t>
+          <t>Data Center Pre Development Project Manager</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>shyftplan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Berlin, Berlin, Germany</t>
-        </is>
-      </c>
+          <t>PRS</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4417935749</t>
+          <t>https://www.linkedin.com/jobs/view/4420972553</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Project Director (Germany)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>Gülermak Renewables</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Stuttgart, Baden-Württemberg, Germany</t>
+          <t>Berlin, Berlin, Germany</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4389905806</t>
+          <t>https://www.linkedin.com/jobs/view/4412808283</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Project Manager Supply Chain (m/f/x)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Thorlabs</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Berlin, Berlin, Germany</t>
+          <t>Bergkirchen, Bavaria, Germany</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4420627609</t>
+          <t>https://www.linkedin.com/jobs/view/4421695474</t>
         </is>
       </c>
     </row>
@@ -861,10 +861,14 @@
           <t>Haystack</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Karlsruhe, Baden-Württemberg, Germany</t>
+        </is>
+      </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4419323365</t>
+          <t>https://www.linkedin.com/jobs/view/4418387894</t>
         </is>
       </c>
     </row>
